--- a/unlockables.xlsx
+++ b/unlockables.xlsx
@@ -3,19 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B996253B-20ED-4CDF-BBB7-80590E7F8F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF0B583-8AF1-41B8-8375-D6A384FC3321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unlockables" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unlockables!$A$1:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase">Unlockables!$A$1:$F$26</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
   <si>
     <t>Room</t>
   </si>
@@ -62,7 +66,7 @@
     <t>Emily's method video, notes to self</t>
   </si>
   <si>
-    <t>Ok. It's Monday night. They just messaged me from practice. They said they could hear Zu singing from where they were. So they were in that room tonight. I wasn't. That's the first real thing I know. Every time they tell me where they are, I'm going to check where everyone else was. That's how I find them.</t>
+    <t>Ok. It's Tuesday morning. They just messaged me from practice. They said they could hear Zulmarie singing from where they were. So they were in that room tonight. I wasn't. That's the first real thing I know. Every time they tell me where they are, I'm going to check where everyone else was. That's how I find them.</t>
   </si>
   <si>
     <t>PRACTICE</t>
@@ -71,6 +75,9 @@
     <t>Video</t>
   </si>
   <si>
+    <t>Pending</t>
+  </si>
+  <si>
     <t>Detective's first voicemail</t>
   </si>
   <si>
@@ -137,9 +144,6 @@
     <t>Winston's sports night video from the gym</t>
   </si>
   <si>
-    <t>Thirty of them. One of me. Come take pictures.</t>
-  </si>
-  <si>
     <t>CONES</t>
   </si>
   <si>
@@ -170,7 +174,10 @@
     <t>Emily's voice memo to Zulmarie</t>
   </si>
   <si>
-    <t>6060</t>
+    <t>Zul. Someone took a picture of us in the parking lot tonight. From across the lot. You were standing right next to me when it came in, so I know it wasn't you. I'm telling you so one person knows I'm not crazy. Don't say anything to anyone.</t>
+  </si>
+  <si>
+    <t>6060D20</t>
   </si>
   <si>
     <t>Detective's voice memo, make the list</t>
@@ -194,12 +201,15 @@
     <t>Emily's last video, notes to self</t>
   </si>
   <si>
-    <t>If you're watching this, I'm gone, and I didn't choose it. I didn't walk anywhere. It's one of the five. I've been talking to all of them. Everything I have is spread across my stuff. Look at where they were, and where everyone else was. Find them. Then find me.</t>
+    <t>If you're listening, I'm gone, and I didn't choose it. I didn't walk anywhere. It's one of the five. I've been talking to all of them. Everything I have is spread across my stuff. Look at where they were, and where everyone else was. Find them. Then find me.</t>
   </si>
   <si>
     <t>LANTERN</t>
   </si>
   <si>
+    <t>Audio</t>
+  </si>
+  <si>
     <t>Annee's voice memo, Always.</t>
   </si>
   <si>
@@ -213,9 +223,6 @@
   </si>
   <si>
     <t>3579</t>
-  </si>
-  <si>
-    <t>Zul. Someone took a picture of us in the parking lot tonight. From across the lot. You were standing right next to me when it came in, so I know it wasn't you. I'm telling you so one person knows I'm not crazy. Don't say anything to anyone.</t>
   </si>
 </sst>
 </file>
@@ -240,7 +247,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,7 +262,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -272,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -280,30 +299,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -651,7 +692,7 @@
     <col min="3" max="3" width="70" customWidth="1"/>
     <col min="4" max="4" width="14" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="54.6328125" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -688,7 +729,7 @@
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -706,7 +747,7 @@
       <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -724,25 +765,28 @@
       <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="8" customFormat="1" ht="56" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
+      <c r="F4" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>17</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -750,16 +794,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -768,32 +812,35 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="F7" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
         <v>2</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>23</v>
+      <c r="B8" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>8</v>
+      <c r="D8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -801,49 +848,55 @@
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="F9" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>27</v>
+      <c r="B10" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="D10" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" s="8" customFormat="1" ht="42" x14ac:dyDescent="0.35">
-      <c r="A11" s="9">
+      <c r="F10" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="9" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
         <v>2</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>29</v>
+      <c r="B11" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>20</v>
+      <c r="D11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -851,228 +904,259 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="F12" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
         <v>3</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>34</v>
+      <c r="B13" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="C13" s="6"/>
-      <c r="D13" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="9" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>3</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="15">
+        <v>3</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" s="8" customFormat="1" ht="28" x14ac:dyDescent="0.35">
-      <c r="A14" s="9">
+      <c r="F15" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
         <v>3</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>3</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
-        <v>3</v>
-      </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="11"/>
+      <c r="D16" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+      <c r="E16" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
         <v>4</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="6"/>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
+      <c r="E17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
         <v>4</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="6"/>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+      <c r="E18" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
         <v>4</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="11"/>
+      <c r="D19" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="8" customFormat="1" ht="56" x14ac:dyDescent="0.35">
-      <c r="A20" s="9">
+      <c r="E19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="9" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
         <v>4</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>4</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
         <v>5</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="10" t="s">
+      <c r="B22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="11"/>
+      <c r="D22" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>5</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="8" customFormat="1" ht="56" x14ac:dyDescent="0.35">
-      <c r="A24" s="9">
+      <c r="F23" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="9" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
         <v>5</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="B24" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" s="8" customFormat="1" ht="28" x14ac:dyDescent="0.35">
-      <c r="A25" s="9">
+      <c r="D24" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="9" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
         <v>5</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>61</v>
+      <c r="B25" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>20</v>
+        <v>64</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -1080,20 +1164,21 @@
         <v>5</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/unlockables.xlsx
+++ b/unlockables.xlsx
@@ -1,17 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF0B583-8AF1-41B8-8375-D6A384FC3321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500"/>
   </bookViews>
   <sheets>
-    <sheet name="Unlockables" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Unlockables" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unlockables!$A$1:$F$26</definedName>
     <definedName name="_xlnm._FilterDatabase">Unlockables!$A$1:$F$26</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -75,109 +73,109 @@
     <t>Video</t>
   </si>
   <si>
+    <t>Detective's first voicemail</t>
+  </si>
+  <si>
+    <t>0917</t>
+  </si>
+  <si>
+    <t>Voice memo</t>
+  </si>
+  <si>
+    <t>Star inside Emily's mailbox</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>Unknown's photo of the back of Emily's head, Six.</t>
+  </si>
+  <si>
+    <t>5190</t>
+  </si>
+  <si>
+    <t>Detective's four stars in evidence bags</t>
+  </si>
+  <si>
+    <t>6271</t>
+  </si>
+  <si>
+    <t>Thursday live stream clip, 7:45 PM</t>
+  </si>
+  <si>
+    <t>LIVESTREAM</t>
+  </si>
+  <si>
+    <t>Will's voice memo, not the group, not MM</t>
+  </si>
+  <si>
+    <t>Emily. It's Will. Listen to me. Do not send those pictures to anybody else. Not the group. Not MM. If you're right, we do not want this in a group chat. If you're wrong, we do not want it anywhere. Let me handle it.</t>
+  </si>
+  <si>
+    <t>7788</t>
+  </si>
+  <si>
+    <t>Unknown's star on the table with the mug</t>
+  </si>
+  <si>
+    <t>5502</t>
+  </si>
+  <si>
+    <t>Doorbell camera, hoodie at the mailbox</t>
+  </si>
+  <si>
+    <t>HOODIE</t>
+  </si>
+  <si>
+    <t>Winston's voice memo, four keys</t>
+  </si>
+  <si>
+    <t>Four keys. Me, Will, MM, and the one in the office. That's it. If you think there's a fifth one out there, you tell me, because that is my problem, not yours.</t>
+  </si>
+  <si>
+    <t>3141</t>
+  </si>
+  <si>
+    <t>Winston's sports night video from the gym</t>
+  </si>
+  <si>
+    <t>CONES</t>
+  </si>
+  <si>
+    <t>Church at night, one window lit</t>
+  </si>
+  <si>
+    <t>9312</t>
+  </si>
+  <si>
+    <t>Pancake crew under the IHOP sign</t>
+  </si>
+  <si>
+    <t>1899</t>
+  </si>
+  <si>
+    <t>Unknown's parking lot photo of Emily and Zulmarie</t>
+  </si>
+  <si>
+    <t>7034</t>
+  </si>
+  <si>
+    <t>Flashlight at the corner of the building</t>
+  </si>
+  <si>
+    <t>8823</t>
+  </si>
+  <si>
+    <t>Emily's voice memo to Zulmarie</t>
+  </si>
+  <si>
+    <t>Zul. Someone took a picture of us in the parking lot tonight. From across the lot. You were standing right next to me when it came in, so I know it wasn't you. I'm telling you so one person knows I'm not crazy. Don't say anything to anyone.</t>
+  </si>
+  <si>
+    <t>6060D20</t>
+  </si>
+  <si>
     <t>Pending</t>
-  </si>
-  <si>
-    <t>Detective's first voicemail</t>
-  </si>
-  <si>
-    <t>0917</t>
-  </si>
-  <si>
-    <t>Voice memo</t>
-  </si>
-  <si>
-    <t>Star inside Emily's mailbox</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>Unknown's photo of the back of Emily's head, Six.</t>
-  </si>
-  <si>
-    <t>5190</t>
-  </si>
-  <si>
-    <t>Detective's four stars in evidence bags</t>
-  </si>
-  <si>
-    <t>6271</t>
-  </si>
-  <si>
-    <t>Thursday live stream clip, 7:45 PM</t>
-  </si>
-  <si>
-    <t>LIVESTREAM</t>
-  </si>
-  <si>
-    <t>Will's voice memo, not the group, not MM</t>
-  </si>
-  <si>
-    <t>Emily. It's Will. Listen to me. Do not send those pictures to anybody else. Not the group. Not MM. If you're right, we do not want this in a group chat. If you're wrong, we do not want it anywhere. Let me handle it.</t>
-  </si>
-  <si>
-    <t>7788</t>
-  </si>
-  <si>
-    <t>Unknown's star on the table with the mug</t>
-  </si>
-  <si>
-    <t>5502</t>
-  </si>
-  <si>
-    <t>Doorbell camera, hoodie at the mailbox</t>
-  </si>
-  <si>
-    <t>HOODIE</t>
-  </si>
-  <si>
-    <t>Winston's voice memo, four keys</t>
-  </si>
-  <si>
-    <t>Four keys. Me, Will, MM, and the one in the office. That's it. If you think there's a fifth one out there, you tell me, because that is my problem, not yours.</t>
-  </si>
-  <si>
-    <t>3141</t>
-  </si>
-  <si>
-    <t>Winston's sports night video from the gym</t>
-  </si>
-  <si>
-    <t>CONES</t>
-  </si>
-  <si>
-    <t>Church at night, one window lit</t>
-  </si>
-  <si>
-    <t>9312</t>
-  </si>
-  <si>
-    <t>Pancake crew under the IHOP sign</t>
-  </si>
-  <si>
-    <t>1899</t>
-  </si>
-  <si>
-    <t>Unknown's parking lot photo of Emily and Zulmarie</t>
-  </si>
-  <si>
-    <t>7034</t>
-  </si>
-  <si>
-    <t>Flashlight at the corner of the building</t>
-  </si>
-  <si>
-    <t>8823</t>
-  </si>
-  <si>
-    <t>Emily's voice memo to Zulmarie</t>
-  </si>
-  <si>
-    <t>Zul. Someone took a picture of us in the parking lot tonight. From across the lot. You were standing right next to me when it came in, so I know it wasn't you. I'm telling you so one person knows I'm not crazy. Don't say anything to anyone.</t>
-  </si>
-  <si>
-    <t>6060D20</t>
   </si>
   <si>
     <t>Detective's voice memo, make the list</t>
@@ -228,14 +226,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -683,9 +681,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -769,7 +767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="9" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="70" customHeight="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -786,7 +784,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -794,14 +792,14 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>9</v>
@@ -812,11 +810,11 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>8</v>
@@ -830,11 +828,11 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>8</v>
@@ -848,11 +846,11 @@
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>8</v>
@@ -866,11 +864,11 @@
         <v>2</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>17</v>
@@ -879,21 +877,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="9" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="42" customHeight="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>2</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="E11" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>9</v>
@@ -904,11 +902,11 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>8</v>
@@ -922,11 +920,11 @@
         <v>3</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>8</v>
@@ -935,36 +933,36 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="9" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="28" customHeight="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>3</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>39</v>
-      </c>
       <c r="E14" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>3</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>17</v>
@@ -978,17 +976,17 @@
         <v>3</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -996,11 +994,11 @@
         <v>4</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>8</v>
@@ -1014,11 +1012,11 @@
         <v>4</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>8</v>
@@ -1032,40 +1030,40 @@
         <v>4</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="9" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>4</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>4</v>
       </c>
@@ -1077,13 +1075,13 @@
         <v>54</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>5</v>
       </c>
@@ -1098,10 +1096,10 @@
         <v>8</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>5</v>
       </c>
@@ -1119,7 +1117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="9" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="56" customHeight="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>5</v>
       </c>
@@ -1136,10 +1134,10 @@
         <v>62</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" s="9" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>5</v>
       </c>
@@ -1153,13 +1151,13 @@
         <v>65</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>5</v>
       </c>
@@ -1171,15 +1169,15 @@
         <v>67</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F26"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>